--- a/Trails_SystemSetting_SCB/Cypress/fixtures/empty.xlsx
+++ b/Trails_SystemSetting_SCB/Cypress/fixtures/empty.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="153222"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Amin\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Amin\Desktop\Scb_folder_files\Trails_SystemSetting_SCB 3\Trails_SystemSetting_SCB 3\Trails_SystemSetting_SCB\Cypress\downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="7480" windowHeight="3060"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="7300"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -21,6 +21,10 @@
     </ext>
   </extLst>
 </workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -90,7 +94,7 @@
         <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent1>
       <a:accent2>
         <a:srgbClr val="ED7D31"/>
@@ -102,7 +106,7 @@
         <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent5>
       <a:accent6>
         <a:srgbClr val="70AD47"/>
@@ -119,9 +123,9 @@
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线 Light"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -149,14 +153,31 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -184,6 +205,23 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -338,6 +376,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="31.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.1796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
